--- a/artfynd/A 4468-2024 artfynd.xlsx
+++ b/artfynd/A 4468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,459 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114784802</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78450</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>765060</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7085692</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>114784805</v>
+      </c>
+      <c r="B5" t="n">
+        <v>82189</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>765037</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7085723</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>114784792</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57248</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>765018</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7085762</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>114784804</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78450</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tavleliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>765039</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7085715</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-02-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Yasmine Kindlund, Joakim Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 4468-2024 artfynd.xlsx
+++ b/artfynd/A 4468-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
